--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1434-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1434-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{283F0BFC-1DB3-49D9-9C40-B311D2484F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AE9B3C2-AE6E-4AFE-B643-384793D92B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{315F8C81-46F3-4432-B724-1C3DD82BA0DB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F73C612C-7DC6-439C-842A-72F623A4D0CA}"/>
   </bookViews>
   <sheets>
     <sheet name="1434-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1634,27 +1634,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6787BAB-9BB5-4524-8342-BCDC545F47B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B3A7E4-A43E-464C-A1F1-9846B9DC3004}">
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1688,7 +1687,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1724,7 +1723,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1776,7 +1775,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1844,7 +1843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1988,7 +1987,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2204,7 +2203,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2276,7 +2275,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2348,7 +2347,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2420,7 +2419,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2564,7 +2563,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2780,7 +2779,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2852,7 +2851,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2996,7 +2995,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>9.8699999999999992</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3140,7 +3139,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3212,7 +3211,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2002</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="18" t="s">
@@ -3528,7 +3527,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2001</v>
       </c>
@@ -3600,7 +3599,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="53"/>
       <c r="B30" s="54"/>
       <c r="C30" s="20" t="s">
@@ -3628,7 +3627,7 @@
       <c r="W30" s="60"/>
       <c r="X30" s="56"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2000</v>
       </c>
@@ -3700,7 +3699,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="43"/>
       <c r="B32" s="44"/>
       <c r="C32" s="18" t="s">
@@ -3728,7 +3727,7 @@
       <c r="W32" s="50"/>
       <c r="X32" s="46"/>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="51">
         <v>1999</v>
       </c>
@@ -3800,7 +3799,7 @@
         <v>8.91</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="53"/>
       <c r="B34" s="54"/>
       <c r="C34" s="20" t="s">
@@ -3828,7 +3827,7 @@
       <c r="W34" s="60"/>
       <c r="X34" s="56"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>1998</v>
       </c>
@@ -3900,7 +3899,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="43"/>
       <c r="B36" s="44"/>
       <c r="C36" s="18" t="s">
@@ -3928,7 +3927,7 @@
       <c r="W36" s="50"/>
       <c r="X36" s="46"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="51">
         <v>1997</v>
       </c>
@@ -4000,7 +3999,7 @@
         <v>7.24</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="53"/>
       <c r="B38" s="54"/>
       <c r="C38" s="20" t="s">
@@ -4028,7 +4027,7 @@
       <c r="W38" s="60"/>
       <c r="X38" s="56"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="41">
         <v>1996</v>
       </c>
@@ -4100,7 +4099,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="43"/>
       <c r="B40" s="44"/>
       <c r="C40" s="18" t="s">
@@ -4128,7 +4127,7 @@
       <c r="W40" s="50"/>
       <c r="X40" s="46"/>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="51">
         <v>1995</v>
       </c>
@@ -4200,7 +4199,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="53"/>
       <c r="B42" s="54"/>
       <c r="C42" s="20" t="s">
@@ -4228,7 +4227,7 @@
       <c r="W42" s="60"/>
       <c r="X42" s="56"/>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>1994</v>
       </c>
@@ -4300,7 +4299,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="43"/>
       <c r="B44" s="44"/>
       <c r="C44" s="18" t="s">
@@ -4328,7 +4327,7 @@
       <c r="W44" s="50"/>
       <c r="X44" s="46"/>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="51">
         <v>1993</v>
       </c>
@@ -4400,7 +4399,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="53"/>
       <c r="B46" s="54"/>
       <c r="C46" s="20" t="s">
@@ -4428,7 +4427,7 @@
       <c r="W46" s="60"/>
       <c r="X46" s="56"/>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
         <v>1992</v>
       </c>
@@ -4500,7 +4499,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="43"/>
       <c r="B48" s="44"/>
       <c r="C48" s="18" t="s">
@@ -4528,7 +4527,7 @@
       <c r="W48" s="50"/>
       <c r="X48" s="46"/>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="51">
         <v>1991</v>
       </c>
@@ -4600,7 +4599,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="53"/>
       <c r="B50" s="54"/>
       <c r="C50" s="20" t="s">
@@ -4628,7 +4627,7 @@
       <c r="W50" s="60"/>
       <c r="X50" s="56"/>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="41">
         <v>1990</v>
       </c>
@@ -4700,7 +4699,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="43"/>
       <c r="B52" s="44"/>
       <c r="C52" s="18" t="s">
@@ -4728,7 +4727,7 @@
       <c r="W52" s="50"/>
       <c r="X52" s="46"/>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="51">
         <v>1989</v>
       </c>
@@ -4800,7 +4799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="53"/>
       <c r="B54" s="54"/>
       <c r="C54" s="20" t="s">
@@ -4828,7 +4827,7 @@
       <c r="W54" s="60"/>
       <c r="X54" s="56"/>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37">
         <v>1988</v>
       </c>
@@ -4900,7 +4899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="39">
         <v>1987</v>
       </c>
@@ -4972,7 +4971,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="37">
         <v>1986</v>
       </c>
@@ -5044,7 +5043,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="39">
         <v>1985</v>
       </c>
@@ -5116,7 +5115,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="37">
         <v>1984</v>
       </c>
@@ -5188,7 +5187,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="39">
         <v>1983</v>
       </c>
@@ -5260,7 +5259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="37" t="s">
         <v>78</v>
       </c>
